--- a/qc/spreadsheets/sharedreward_qc.xlsx
+++ b/qc/spreadsheets/sharedreward_qc.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'runs'!$A$1:$Y$669</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'thresholds'!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25294,7 +25294,7 @@
         <v>0.5</v>
       </c>
       <c r="L272" t="n">
-        <v>99.88442531484138</v>
+        <v>99.90435198469632</v>
       </c>
       <c r="M272" t="b">
         <v>0</v>
@@ -25385,7 +25385,7 @@
         <v>0.4642857142857143</v>
       </c>
       <c r="L273" t="n">
-        <v>99.93357776715023</v>
+        <v>99.86317020032945</v>
       </c>
       <c r="M273" t="b">
         <v>0</v>
@@ -25476,7 +25476,7 @@
         <v>0.5</v>
       </c>
       <c r="L274" t="n">
-        <v>99.91365109729529</v>
+        <v>99.9096657633243</v>
       </c>
       <c r="M274" t="b">
         <v>0</v>
@@ -25567,7 +25567,7 @@
         <v>0.4090909090909091</v>
       </c>
       <c r="L275" t="n">
-        <v>99.85785642170147</v>
+        <v>99.94420532440618</v>
       </c>
       <c r="M275" t="b">
         <v>0</v>
@@ -26032,7 +26032,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="L280" t="n">
-        <v>99.90036665072533</v>
+        <v>99.86582708964345</v>
       </c>
       <c r="M280" t="b">
         <v>0</v>
@@ -26123,7 +26123,7 @@
         <v>0.3181818181818182</v>
       </c>
       <c r="L281" t="n">
-        <v>99.89372442744035</v>
+        <v>99.86582708964345</v>
       </c>
       <c r="M281" t="b">
         <v>0</v>
@@ -26578,7 +26578,7 @@
         <v>0.3548387096774194</v>
       </c>
       <c r="L286" t="n">
-        <v>99.78479196556671</v>
+        <v>99.79276263350869</v>
       </c>
       <c r="M286" t="b">
         <v>0</v>
@@ -26669,7 +26669,7 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="L287" t="n">
-        <v>99.73165417928689</v>
+        <v>99.7608799617408</v>
       </c>
       <c r="M287" t="b">
         <v>0</v>
@@ -28772,7 +28772,7 @@
         <v>0.3928571428571428</v>
       </c>
       <c r="L310" t="n">
-        <v>99.80339019076466</v>
+        <v>99.73696795791487</v>
       </c>
       <c r="M310" t="b">
         <v>0</v>
@@ -28863,7 +28863,7 @@
         <v>0.4210526315789473</v>
       </c>
       <c r="L311" t="n">
-        <v>99.84324353047452</v>
+        <v>99.77283596365375</v>
       </c>
       <c r="M311" t="b">
         <v>0</v>
@@ -61972,20 +61972,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -61996,50 +61998,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>bids_tasks</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>iqr</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>lower_fence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>upper_fence</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>outlier_direction</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>n_outliers</t>
         </is>
@@ -62058,33 +62070,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sharedreward</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>tsnr</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>668</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>23.82815003744327</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>38.75556830753339</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>14.92741827009013</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>1.437022632308071</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>61.14669571266859</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -62101,33 +62123,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sharedreward</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>fd_mean</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>668</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>0.1184472027763173</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.2403255835369235</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.1218783807606062</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>-0.06437036836459194</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.4231431546778327</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>36</v>
       </c>
     </row>
@@ -62144,33 +62176,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sharedreward</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>tedana_rejected_components</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>668</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>21</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>-9</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>39</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>56</v>
       </c>
     </row>
@@ -62187,38 +62229,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sharedreward</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>brain_coverage_pct</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>668</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>99.60412349221531</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>99.90568042935331</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.3015569371380025</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>99.1517880865083</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>100.3580158350603</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:M5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>